--- a/audit_log.xlsx
+++ b/audit_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,6 +538,586 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-29T19:23:32</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:05:09</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:06:46</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:08:11</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:10:40</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:21:00</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:33:15</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:34:05</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-29T21:55:04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:02:34</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:02:54</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>patient_id=PP-000001, result=0, prob=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:03:43</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:03:52</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:09:44</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:10:18</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>patient_id=PP-000001, result=0, prob=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:11:05</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:14:48</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:14:56</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:16:19</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:19:14</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:31:39</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:38:28</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:42:29</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:43:58</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:47:05</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:50:07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:05:47</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>email=isammohamed781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:17:44</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:28:46</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_log.xlsx
+++ b/audit_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,6 +1118,206 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:42:39</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:52:23</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:56:37</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:11:05</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:31:47</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:41:25</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:34:11</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:36:00</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:50:36</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:50:51</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>patient_id=26092901, result=0, prob=0.14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_log.xlsx
+++ b/audit_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1318,6 +1318,206 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:51:27</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:09:26</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:10:05</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:18:34</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:23:17</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:48:42</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:54:08</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>patient_id=26100101, result=0, prob=0.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:54:09</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>patient_id=26100101, result=0, prob=0.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-01T04:09:28</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>email=isammohd781@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-01T04:11:07</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>predict</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>patient_id=26100101, result=1, prob=0.89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
